--- a/artfynd/A 7698-2024 artfynd.xlsx
+++ b/artfynd/A 7698-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -810,6 +810,144 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>115106271</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97560</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Erik-Bengtsstugan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>504854</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7007976</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-07-09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-07-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Minst 1 st stjälk av brudsporre på en delvis igenväxt gräsmark med spår av tidigare hävd. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7698-2024.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Frisk gräsmark med lövträd</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>En äldre delvis igenväxt infartsväg med fältskikt dominerat av gräs och örter med spår av tidigare hävd med flertalet hävdgynnade arter. Trädskikt av asp, tall, sälg och björk. På frisk mark enligt markfuktighetsdata.</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7698-2024 artfynd.xlsx
+++ b/artfynd/A 7698-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -949,6 +949,220 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123451254</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97402</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Svarttjärnen, 975 m N om i vägkanter på väg 744, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>504897</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7008131</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1993-06-24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1993-06-24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikstaxruta 19F2c13</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123451229</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101760</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Svarttjärnen, 975 m N om i vägkanter på väg 744, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>504897</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7008131</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>1993-06-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1993-06-24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikstaxruta 19F2c13</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7698-2024 artfynd.xlsx
+++ b/artfynd/A 7698-2024 artfynd.xlsx
@@ -951,10 +951,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123451254</v>
+        <v>123451229</v>
       </c>
       <c r="B4" t="n">
-        <v>97402</v>
+        <v>101766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -967,21 +967,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222112</v>
+        <v>221343</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1058,10 +1058,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123451229</v>
+        <v>123451254</v>
       </c>
       <c r="B5" t="n">
-        <v>101760</v>
+        <v>97409</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221343</v>
+        <v>222112</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>

--- a/artfynd/A 7698-2024 artfynd.xlsx
+++ b/artfynd/A 7698-2024 artfynd.xlsx
@@ -954,7 +954,7 @@
         <v>123451254</v>
       </c>
       <c r="B4" t="n">
-        <v>97412</v>
+        <v>97429</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>123451229</v>
       </c>
       <c r="B5" t="n">
-        <v>101769</v>
+        <v>101786</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 7698-2024 artfynd.xlsx
+++ b/artfynd/A 7698-2024 artfynd.xlsx
@@ -954,7 +954,7 @@
         <v>123451254</v>
       </c>
       <c r="B4" t="n">
-        <v>97429</v>
+        <v>97446</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>123451229</v>
       </c>
       <c r="B5" t="n">
-        <v>101786</v>
+        <v>101804</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 7698-2024 artfynd.xlsx
+++ b/artfynd/A 7698-2024 artfynd.xlsx
@@ -951,10 +951,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123451254</v>
+        <v>123451229</v>
       </c>
       <c r="B4" t="n">
-        <v>97446</v>
+        <v>101806</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -967,21 +967,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222112</v>
+        <v>221343</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1058,10 +1058,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123451229</v>
+        <v>123451254</v>
       </c>
       <c r="B5" t="n">
-        <v>101804</v>
+        <v>97448</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221343</v>
+        <v>222112</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>

--- a/artfynd/A 7698-2024 artfynd.xlsx
+++ b/artfynd/A 7698-2024 artfynd.xlsx
@@ -951,10 +951,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123451229</v>
+        <v>123451254</v>
       </c>
       <c r="B4" t="n">
-        <v>101806</v>
+        <v>97023</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -967,21 +967,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221343</v>
+        <v>222112</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1058,10 +1058,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123451254</v>
+        <v>123451229</v>
       </c>
       <c r="B5" t="n">
-        <v>97448</v>
+        <v>101381</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222112</v>
+        <v>221343</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>

--- a/artfynd/A 7698-2024 artfynd.xlsx
+++ b/artfynd/A 7698-2024 artfynd.xlsx
@@ -951,10 +951,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123451254</v>
+        <v>123451229</v>
       </c>
       <c r="B4" t="n">
-        <v>97023</v>
+        <v>101381</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -967,21 +967,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222112</v>
+        <v>221343</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1058,10 +1058,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123451229</v>
+        <v>123451254</v>
       </c>
       <c r="B5" t="n">
-        <v>101381</v>
+        <v>97023</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221343</v>
+        <v>222112</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>

--- a/artfynd/A 7698-2024 artfynd.xlsx
+++ b/artfynd/A 7698-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115106271</v>
+        <v>118432860</v>
       </c>
       <c r="B2" t="n">
-        <v>97652</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219811</v>
+        <v>201129</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Lycaena virgaureae</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,20 +708,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -735,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504854</v>
+        <v>504861</v>
       </c>
       <c r="R2" t="n">
-        <v>7007976</v>
+        <v>7007922</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,17 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-07-09</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-07-09</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Minst 1 st stjälk av brudsporre på en delvis igenväxt gräsmark med spår av tidigare hävd. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7698-2024.</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,44 +763,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Frisk gräsmark med lövträd</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>En äldre delvis igenväxt infartsväg med fältskikt dominerat av gräs och örter med spår av tidigare hävd med flertalet hävdgynnade arter. Trädskikt av asp, tall, sälg och björk. På frisk mark enligt markfuktighetsdata.</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tobias Nykänen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tobias Nykänen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115106196</v>
+        <v>115106271</v>
       </c>
       <c r="B3" t="n">
-        <v>97673</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -829,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -913,7 +876,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Minst 1 st stjälk av tvåblad på en delvis igenväxt gräsmark med spår av tidigare hävd. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7698-2024.</t>
+          <t>Minst 1 st stjälk av brudsporre på en delvis igenväxt gräsmark med spår av tidigare hävd. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7698-2024.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -951,53 +914,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123451229</v>
+        <v>118432648</v>
       </c>
       <c r="B4" t="n">
-        <v>101403</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221343</v>
+        <v>219811</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svarttjärnen, 975 m N om i vägkanter på väg 744, Jmt</t>
+          <t>Erik-Bengtsstugan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504897</v>
+        <v>504861</v>
       </c>
       <c r="R4" t="n">
-        <v>7008131</v>
+        <v>7007922</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1021,17 +979,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1993-06-24</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1993-06-24</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikstaxruta 19F2c13</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1046,65 +999,80 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Tobias Nykänen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Tobias Nykänen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123451254</v>
+        <v>115106196</v>
       </c>
       <c r="B5" t="n">
-        <v>97045</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222112</v>
+        <v>219847</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svarttjärnen, 975 m N om i vägkanter på väg 744, Jmt</t>
+          <t>Erik-Bengtsstugan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504897</v>
+        <v>504854</v>
       </c>
       <c r="R5" t="n">
-        <v>7008131</v>
+        <v>7007976</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,17 +1096,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1993-06-24</t>
+          <t>2023-07-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1993-06-24</t>
+          <t>2023-07-09</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikstaxruta 19F2c13</t>
+          <t>Minst 1 st stjälk av tvåblad på en delvis igenväxt gräsmark med spår av tidigare hävd. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7698-2024.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,21 +1115,333 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Frisk gräsmark med lövträd</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>En äldre delvis igenväxt infartsväg med fältskikt dominerat av gräs och örter med spår av tidigare hävd med flertalet hävdgynnade arter. Trädskikt av asp, tall, sälg och björk. På frisk mark enligt markfuktighetsdata.</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>118432636</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Erik-Bengtsstugan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>504861</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7007922</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tobias Nykänen</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tobias Nykänen</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123451229</v>
+      </c>
+      <c r="B7" t="n">
+        <v>102464</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Svarttjärnen, 975 m N om i vägkanter på väg 744, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>504897</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7008131</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>1993-06-24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>1993-06-24</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikstaxruta 19F2c13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Staffan Åström</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Lars-Åke Bäckström</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123451254</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Svarttjärnen, 975 m N om i vägkanter på väg 744, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>504897</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7008131</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>1993-06-24</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>1993-06-24</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikstaxruta 19F2c13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7698-2024 artfynd.xlsx
+++ b/artfynd/A 7698-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118432860</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -911,6 +921,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115106271</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118432648</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1141,6 +1161,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115106196</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1238,6 +1263,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118432636</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1340,6 +1370,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123451229</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1442,8 +1477,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123451254</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>